--- a/TestData/T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
+++ b/TestData/T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20389"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98990376-FD3C-4A00-99C5-AB054ED8E298}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CA3948-2997-4039-A702-BE966395A391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="6804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Company" sheetId="1" r:id="rId1"/>
-    <sheet name="Contact" sheetId="2" r:id="rId2"/>
-    <sheet name="GiftLog" sheetId="4" r:id="rId3"/>
-    <sheet name="GiftLogComboBox" sheetId="6" r:id="rId4"/>
-    <sheet name="Users" sheetId="5" r:id="rId5"/>
+    <sheet name="Users" sheetId="5" r:id="rId1"/>
+    <sheet name="AppName" sheetId="7" r:id="rId2"/>
+    <sheet name="Company" sheetId="1" r:id="rId3"/>
+    <sheet name="Contact" sheetId="2" r:id="rId4"/>
+    <sheet name="GiftLog" sheetId="4" r:id="rId5"/>
+    <sheet name="GiftLogComboBox" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
   <si>
     <t>Report</t>
   </si>
@@ -215,6 +216,12 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
   </si>
 </sst>
 </file>
@@ -258,13 +265,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -545,6 +551,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C1A4194-07F7-4B4A-B892-397CC42812D5}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -633,7 +686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -684,7 +737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -703,37 +756,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -744,7 +797,7 @@
       <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D2" t="s">
@@ -778,7 +831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -788,55 +841,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="3"/>
+      <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -933,28 +986,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>